--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486662_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486662_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5092</v>
+        <v>6.7008</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1022</v>
+        <v>4.4677</v>
       </c>
       <c r="F2" t="n">
-        <v>2.407</v>
+        <v>2.2331</v>
       </c>
       <c r="G2" t="n">
         <v>2.1299</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6496</v>
+        <v>1.8412</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6891</v>
+        <v>1.0546</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9605</v>
+        <v>0.7866</v>
       </c>
       <c r="V2" t="n">
         <v>1.1851</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0506</v>
+        <v>4.2219</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7247</v>
+        <v>2.3405</v>
       </c>
       <c r="F3" t="n">
-        <v>1.326</v>
+        <v>1.8813</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9639</v>
+        <v>1.0162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7726</v>
+        <v>1.8075</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1913</v>
+        <v>-0.7913</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9716</v>
+        <v>2.6246</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6694</v>
+        <v>2.4979</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3022</v>
+        <v>0.1267</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0077</v>
+        <v>-1.6083</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8969</v>
+        <v>-0.6904</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1108</v>
+        <v>-0.9179</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.4068</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4409</v>
+        <v>0.8133</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2098</v>
+        <v>0.5935</v>
       </c>
       <c r="V3" t="n">
-        <v>0.243</v>
+        <v>1.7989</v>
       </c>
       <c r="W3" t="n">
-        <v>0.243</v>
+        <v>1.7989</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0398</v>
+        <v>3.4178</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4235</v>
+        <v>-0.3684</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4634</v>
+        <v>3.7862</v>
       </c>
       <c r="G4" t="n">
         <v>-0.838</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9045</v>
+        <v>1.2824</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3028</v>
+        <v>0.358</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6016</v>
+        <v>0.9244</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6443</v>
+        <v>2.8893</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8375</v>
+        <v>1.4144</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8069</v>
+        <v>1.475</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0162</v>
+        <v>1.9639</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8075</v>
+        <v>0.7726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7913</v>
+        <v>1.1913</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6246</v>
+        <v>2.9716</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4979</v>
+        <v>1.6694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1267</v>
+        <v>1.3022</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6083</v>
+        <v>-1.0077</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6904</v>
+        <v>-0.8969</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9179</v>
+        <v>-0.1108</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8962</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1708</v>
+        <v>0.4894</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6898</v>
+        <v>0.1306</v>
       </c>
       <c r="U5" t="n">
-        <v>0.519</v>
+        <v>0.3588</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7989</v>
+        <v>0.243</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7989</v>
+        <v>0.243</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1078</v>
+        <v>1.6997</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2689</v>
+        <v>-0.0897</v>
       </c>
       <c r="F6" t="n">
-        <v>1.839</v>
+        <v>1.7893</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2143</v>
@@ -922,13 +922,13 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4493</v>
+        <v>2.0411</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6545</v>
+        <v>1.296</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7947</v>
+        <v>0.7451</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8623</v>
+        <v>0.399</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6612</v>
+        <v>0.2475</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2011</v>
+        <v>0.1514</v>
       </c>
       <c r="G7" t="n">
         <v>0.4958</v>
@@ -1000,13 +1000,13 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8219</v>
+        <v>0.3586</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.1654</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2428</v>
+        <v>0.1931</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2277</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>D. CABRERA CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.594</v>
+        <v>0.1931</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1275</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7216</v>
+        <v>0.1931</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5516</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.6058</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0542</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4469</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.4673</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0204</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1047</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1385</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0338</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.4754</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.827</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2349</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2469</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.988</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CABRERA CABRERA</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1931</v>
+        <v>-1.5931</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-2.1408</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1931</v>
+        <v>0.5477</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.5516</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-3.6058</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.0542</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.4469</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-3.4673</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.0204</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.1047</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1385</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.0338</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>-3.4754</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.827</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.0478</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2336</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.8142</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8212</v>
+        <v>-1.9649</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7776</v>
+        <v>-2.8469</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9565</v>
+        <v>0.882</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7306</v>
@@ -1234,13 +1234,13 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0333</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3863</v>
+        <v>0.5445</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4196</v>
+        <v>0.3451</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0352</v>
+        <v>-2.543</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3006</v>
+        <v>-3.7835</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2654</v>
+        <v>1.2406</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3043</v>
@@ -1312,13 +1312,13 @@
         <v>2.3169</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4027</v>
+        <v>0.0896</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7725</v>
+        <v>-0.2554</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3698</v>
+        <v>0.345</v>
       </c>
       <c r="V11" t="n">
         <v>0.2856</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.1447</v>
+        <v>13.4206</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0347</v>
+        <v>-0.7592000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>14.18</v>
+        <v>14.1797</v>
       </c>
       <c r="G12" t="n">
         <v>-1.032999999999999</v>
@@ -1390,19 +1390,19 @@
         <v>18.3424</v>
       </c>
       <c r="S12" t="n">
-        <v>11.1707</v>
+        <v>11.4465</v>
       </c>
       <c r="T12" t="n">
-        <v>6.0647</v>
+        <v>6.340600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>5.105799999999999</v>
+        <v>5.1058</v>
       </c>
       <c r="V12" t="n">
         <v>2.042</v>
       </c>
       <c r="W12" t="n">
-        <v>5.0259</v>
+        <v>5.025899999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-2.984</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>L. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5446</v>
+        <v>2.4119</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8799</v>
+        <v>2.2128</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3353</v>
+        <v>0.1991</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2998</v>
+        <v>1.7635</v>
       </c>
       <c r="H13" t="n">
-        <v>2.538</v>
+        <v>2.2134</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7618</v>
+        <v>-0.4499</v>
       </c>
       <c r="J13" t="n">
-        <v>6.405</v>
+        <v>1.399</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8149</v>
+        <v>2.0071</v>
       </c>
       <c r="L13" t="n">
-        <v>3.5901</v>
+        <v>-0.6081</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1052</v>
+        <v>0.3645</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2769</v>
+        <v>0.2063</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1717</v>
+        <v>0.1582</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.827</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4962</v>
+        <v>-0.5101</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.497</v>
+        <v>-0.4139</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0008</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7989</v>
+        <v>1.2277</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.741</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. FLORES LUCAS</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0008</v>
+        <v>1.9791</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2128</v>
+        <v>2.6731</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.212</v>
+        <v>-0.694</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7635</v>
+        <v>6.2998</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2134</v>
+        <v>2.538</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4499</v>
+        <v>3.7618</v>
       </c>
       <c r="J14" t="n">
-        <v>1.399</v>
+        <v>6.405</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0071</v>
+        <v>2.8149</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6081</v>
+        <v>3.5901</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3645</v>
+        <v>-0.1052</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2063</v>
+        <v>-0.2769</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1582</v>
+        <v>0.1717</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1585</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.827</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1585</v>
+        <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9212</v>
+        <v>-1.0618</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4139</v>
+        <v>-0.7038</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5073</v>
+        <v>-0.3579</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2277</v>
+        <v>1.7989</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2277</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5998</v>
+        <v>1.2606</v>
       </c>
       <c r="E15" t="n">
-        <v>1.178</v>
+        <v>0.7643</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4218</v>
+        <v>0.4963</v>
       </c>
       <c r="G15" t="n">
         <v>0.8607</v>
@@ -1624,13 +1624,13 @@
         <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1599</v>
+        <v>-0.1793</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5239</v>
+        <v>0.1102</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.364</v>
+        <v>-0.2895</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2124</v>
+        <v>0.4689</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9096</v>
+        <v>-0.7028</v>
       </c>
       <c r="F16" t="n">
-        <v>1.122</v>
+        <v>1.1717</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7861</v>
@@ -1702,13 +1702,13 @@
         <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5115</v>
+        <v>-1.255</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5795</v>
+        <v>-0.3726</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8824</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1826</v>
+        <v>-0.0047</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2842</v>
+        <v>-0.1808</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1016</v>
+        <v>0.1761</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0294</v>
@@ -1780,13 +1780,13 @@
         <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0261</v>
+        <v>-0.8482</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3863</v>
+        <v>-0.2829</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6398</v>
+        <v>-0.5653</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3022</v>
+        <v>-0.2277</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0138</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2884</v>
+        <v>-0.2139</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0209</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2813</v>
+        <v>-0.2068</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6146</v>
+        <v>-0.5898</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9383</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3237</v>
+        <v>0.3485</v>
       </c>
       <c r="G19" t="n">
         <v>1.2818</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0828</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0167</v>
+        <v>0.0415</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2866</v>
+        <v>-2.0093</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2717</v>
+        <v>-3.1683</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9851</v>
+        <v>1.159</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5969</v>
@@ -2014,13 +2014,13 @@
         <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5392</v>
+        <v>-1.262</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.883</v>
+        <v>-0.7796</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6562</v>
+        <v>-0.4824</v>
       </c>
       <c r="V20" t="n">
         <v>0.6565</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9822</v>
+        <v>-2.4596</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9242</v>
+        <v>-2.614</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.058</v>
+        <v>0.1544</v>
       </c>
       <c r="G21" t="n">
         <v>0.8946</v>
@@ -2092,13 +2092,13 @@
         <v>2.8962</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6258</v>
+        <v>-2.1031</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2141</v>
+        <v>-0.9039</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4117</v>
+        <v>-1.1993</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5328</v>
+        <v>-6.1135</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8644</v>
+        <v>-4.6576</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6684</v>
+        <v>-1.456</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0475</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9639</v>
+        <v>-1.5447</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9657</v>
+        <v>-0.7589</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9982</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9421</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6014</v>
+        <v>-7.1711</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.2442</v>
+        <v>-7.5545</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6428</v>
+        <v>0.3834</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5865</v>
@@ -2248,13 +2248,13 @@
         <v>2.7031</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8991</v>
+        <v>-1.4687</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5522</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3469</v>
+        <v>-0.6063</v>
       </c>
       <c r="V23" t="n">
         <v>0.0426</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.1448</v>
+        <v>-12.4552</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.1797</v>
+        <v>-14.1799</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0349</v>
+        <v>1.7246</v>
       </c>
       <c r="G24" t="n">
         <v>1.0331</v>
@@ -2326,13 +2326,13 @@
         <v>17.3771</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.1706</v>
+        <v>-10.481</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.1058</v>
+        <v>-5.105799999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.064699999999999</v>
+        <v>-5.3752</v>
       </c>
       <c r="V24" t="n">
         <v>-2.0419</v>
